--- a/test/session--empty-statements/reference/2 semester 15 subjects/рік/25-3/Відомості 25-3.xlsx
+++ b/test/session--empty-statements/reference/2 semester 15 subjects/рік/25-3/Відомості 25-3.xlsx
@@ -27,7 +27,7 @@
     <definedName name="Ф80" localSheetId="3">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Зведена G7'!$C$3:$T$35</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcMode="autoNoTable" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511" calcMode="autoNoTable" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="F53" s="63">
-        <f>IF(F50="Очікую","Очікую",IF(F50-COUNTIF($U$10:$U44," - ")&lt;ROUNDDOWN(F50*0.4,0),F50-COUNTIF($U$10:$U44," - "),ROUNDDOWN(F50*0.4,0)))</f>
+        <f>IF(F50="Очікую","Очікую",IF(F50-COUNTIF($U$10:$U44," - ")&lt;ROUNDDOWN(F50*0.45,0),F50-COUNTIF($U$10:$U44," - "),ROUNDDOWN(F50*0.45,0)))</f>
         <v/>
       </c>
       <c r="G53" s="6" t="n"/>
@@ -3197,7 +3197,7 @@
       <c r="O53" s="6" t="n"/>
       <c r="P53" s="54" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q53" s="54" t="n"/>
@@ -3487,7 +3487,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності E2 ««Екологія»»</t>
+          <t>Успішності студентів спеціальності E2 «Екологія»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="F28" s="63">
-        <f>IF(F25="Очікую","Очікую",IF(F25-COUNTIF($U$10:$U19," - ")&lt;ROUNDDOWN(F25*0.4,0),F25-COUNTIF($U$10:$U19," - "),ROUNDDOWN(F25*0.4,0)))</f>
+        <f>IF(F25="Очікую","Очікую",IF(F25-COUNTIF($U$10:$U19," - ")&lt;ROUNDDOWN(F25*0.45,0),F25-COUNTIF($U$10:$U19," - "),ROUNDDOWN(F25*0.45,0)))</f>
         <v/>
       </c>
       <c r="G28" s="6" t="n"/>
@@ -4913,7 +4913,7 @@
       <c r="O28" s="6" t="n"/>
       <c r="P28" s="56" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q28" s="54" t="n"/>
@@ -5232,7 +5232,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності G1 ««Хімічні технології та інженерія»»</t>
+          <t>Успішності студентів спеціальності G1 «Хімічні технології та інженерія»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="F26" s="63">
-        <f>IF(F23="Очікую","Очікую",IF(F23-COUNTIF($U$10:$U17," - ")&lt;ROUNDDOWN(F23*0.4,0),F23-COUNTIF($U$10:$U17," - "),ROUNDDOWN(F23*0.4,0)))</f>
+        <f>IF(F23="Очікую","Очікую",IF(F23-COUNTIF($U$10:$U17," - ")&lt;ROUNDDOWN(F23*0.45,0),F23-COUNTIF($U$10:$U17," - "),ROUNDDOWN(F23*0.45,0)))</f>
         <v/>
       </c>
       <c r="G26" s="6" t="n"/>
@@ -6496,7 +6496,7 @@
       <c r="O26" s="6" t="n"/>
       <c r="P26" s="56" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q26" s="54" t="n"/>
@@ -6817,7 +6817,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності G7 ««Автоматизація, комп'ютерно-інтегровані технології та робототехніка»»</t>
+          <t>Успішності студентів спеціальності G7 «Автоматизація, комп'ютерно-інтегровані технології та робототехніка»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -8792,7 +8792,7 @@
         </is>
       </c>
       <c r="F35" s="63">
-        <f>IF(F32="Очікую","Очікую",IF(F32-COUNTIF($U$10:$U26," - ")&lt;ROUNDDOWN(F32*0.4,0),F32-COUNTIF($U$10:$U26," - "),ROUNDDOWN(F32*0.4,0)))</f>
+        <f>IF(F32="Очікую","Очікую",IF(F32-COUNTIF($U$10:$U26," - ")&lt;ROUNDDOWN(F32*0.45,0),F32-COUNTIF($U$10:$U26," - "),ROUNDDOWN(F32*0.45,0)))</f>
         <v/>
       </c>
       <c r="G35" s="6" t="n"/>
@@ -8810,7 +8810,7 @@
       <c r="O35" s="6" t="n"/>
       <c r="P35" s="56" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q35" s="54" t="n"/>
